--- a/data/trans_orig/barthel-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/barthel-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de dependencia funcional para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Puntuación media de la escala de dependencia funcional para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,78; 99,27</t>
+          <t>92,27; 99,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,41; 98,49</t>
+          <t>93,73; 98,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,06; 96,85</t>
+          <t>87,91; 96,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97,82; 99,52</t>
+          <t>97,72; 99,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,75; 99,72</t>
+          <t>92,92; 99,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,29; 91,38</t>
+          <t>80,75; 91,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,67; 94,69</t>
+          <t>85,53; 94,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92,41; 97,36</t>
+          <t>91,96; 97,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,77; 99,18</t>
+          <t>94,8; 99,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87,97; 94,61</t>
+          <t>88,2; 94,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88,5; 94,94</t>
+          <t>88,67; 94,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,42; 98,27</t>
+          <t>95,21; 98,26</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,33; 99,42</t>
+          <t>94,76; 99,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,97; 96,96</t>
+          <t>88,72; 97,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,89; 99,19</t>
+          <t>94,74; 99,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,15; 97,89</t>
+          <t>92,0; 97,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,16; 97,44</t>
+          <t>91,15; 97,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,12; 92,38</t>
+          <t>82,97; 92,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,54; 96,01</t>
+          <t>89,6; 96,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,44; 92,58</t>
+          <t>87,07; 92,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>93,64; 97,79</t>
+          <t>93,85; 97,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86,74; 93,47</t>
+          <t>87,4; 93,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92,98; 96,93</t>
+          <t>92,52; 96,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,14; 94,07</t>
+          <t>90,1; 94,07</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,66; 99,65</t>
+          <t>93,72; 99,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,23; 96,5</t>
+          <t>83,48; 96,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,51; 98,93</t>
+          <t>90,95; 98,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,57; 94,74</t>
+          <t>88,28; 94,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92,91; 98,17</t>
+          <t>92,6; 97,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,5; 93,52</t>
+          <t>82,72; 93,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,72; 98,23</t>
+          <t>85,23; 98,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,65; 92,57</t>
+          <t>86,68; 92,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,35; 98,34</t>
+          <t>94,58; 98,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,47; 93,77</t>
+          <t>85,06; 93,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90,16; 97,84</t>
+          <t>91,39; 97,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88,83; 92,83</t>
+          <t>88,61; 92,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,28; 99,69</t>
+          <t>94,94; 99,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,73; 97,91</t>
+          <t>91,76; 97,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,64; 97,59</t>
+          <t>92,25; 97,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97,12; 98,79</t>
+          <t>97,04; 98,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,28; 97,8</t>
+          <t>93,31; 97,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,37; 96,2</t>
+          <t>91,01; 96,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,23; 97,16</t>
+          <t>93,35; 97,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,17; 95,49</t>
+          <t>91,97; 95,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,37; 98,38</t>
+          <t>95,61; 98,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,6; 96,49</t>
+          <t>92,69; 96,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93,83; 96,91</t>
+          <t>93,75; 96,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,54; 96,69</t>
+          <t>94,61; 96,71</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,29; 96,72</t>
+          <t>82,52; 96,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,18; 97,1</t>
+          <t>84,72; 97,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93,01; 99,62</t>
+          <t>93,06; 99,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,96; 96,57</t>
+          <t>90,92; 96,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,23; 96,23</t>
+          <t>81,81; 96,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,54; 94,74</t>
+          <t>85,75; 94,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,2; 95,46</t>
+          <t>87,16; 95,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,27; 94,11</t>
+          <t>88,59; 93,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85,05; 95,13</t>
+          <t>85,47; 95,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,82; 95,2</t>
+          <t>87,59; 94,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91,79; 97,07</t>
+          <t>91,79; 97,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>90,24; 94,46</t>
+          <t>90,48; 94,57</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95,5; 99,29</t>
+          <t>95,09; 99,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,14; 97,61</t>
+          <t>88,26; 97,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,85; 94,75</t>
+          <t>85,2; 94,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90,18; 95,54</t>
+          <t>90,23; 95,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,86; 98,25</t>
+          <t>91,87; 98,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84,06; 94,54</t>
+          <t>84,46; 94,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>81,91; 93,28</t>
+          <t>81,8; 93,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,58; 90,58</t>
+          <t>83,9; 90,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94,55; 98,33</t>
+          <t>94,14; 98,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88,09; 95,29</t>
+          <t>88,35; 95,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84,87; 92,96</t>
+          <t>85,37; 93,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88,03; 92,21</t>
+          <t>87,89; 92,18</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,07; 99,44</t>
+          <t>95,58; 99,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>89,08; 97,29</t>
+          <t>88,75; 97,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92,03; 97,26</t>
+          <t>91,98; 97,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95,63; 98,25</t>
+          <t>95,8; 98,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,18; 98,82</t>
+          <t>92,98; 98,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,67; 95,28</t>
+          <t>89,9; 95,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,98; 94,67</t>
+          <t>89,03; 94,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,32; 99,15</t>
+          <t>91,42; 99,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,62; 98,83</t>
+          <t>95,73; 98,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90,97; 95,39</t>
+          <t>91,09; 95,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,42; 95,33</t>
+          <t>91,43; 95,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,22; 99,09</t>
+          <t>94,26; 99,03</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>94,07; 97,9</t>
+          <t>94,07; 97,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,68; 98,95</t>
+          <t>94,66; 98,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95,52; 98,67</t>
+          <t>95,84; 98,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96,62; 98,58</t>
+          <t>96,61; 98,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>91,18; 96,37</t>
+          <t>91,31; 96,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,58; 95,45</t>
+          <t>89,99; 95,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,51; 97,57</t>
+          <t>93,76; 97,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>92,86; 95,78</t>
+          <t>92,71; 95,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>93,17; 96,64</t>
+          <t>93,19; 96,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92,79; 96,55</t>
+          <t>92,6; 96,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95,14; 97,69</t>
+          <t>95,27; 97,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,99; 96,87</t>
+          <t>95,15; 96,83</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>96,28; 98,04</t>
+          <t>96,43; 98,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>93,51; 96,26</t>
+          <t>93,78; 96,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95,12; 97,0</t>
+          <t>95,22; 97,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95,61; 96,91</t>
+          <t>95,55; 96,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>94,41; 96,51</t>
+          <t>94,39; 96,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,78; 92,64</t>
+          <t>89,75; 92,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,27; 94,69</t>
+          <t>92,21; 94,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92,05; 96,47</t>
+          <t>92,04; 96,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>95,6; 96,98</t>
+          <t>95,54; 96,95</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91,91; 93,85</t>
+          <t>91,85; 93,82</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93,8; 95,39</t>
+          <t>93,88; 95,48</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93,93; 96,49</t>
+          <t>93,89; 96,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/barthel-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/barthel-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98,98</t>
+          <t>99,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>95,59</t>
+          <t>95,79</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,18</t>
+          <t>97,36</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,27; 99,28</t>
+          <t>92,02; 99,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,73; 98,54</t>
+          <t>93,51; 98,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,91; 96,66</t>
+          <t>88,82; 96,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97,72; 99,5</t>
+          <t>97,76; 99,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,92; 99,71</t>
+          <t>93,16; 99,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,75; 91,53</t>
+          <t>80,89; 91,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,53; 94,78</t>
+          <t>84,7; 94,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,96; 97,54</t>
+          <t>93,11; 97,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,8; 99,07</t>
+          <t>94,61; 99,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88,2; 94,44</t>
+          <t>88,13; 94,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88,67; 94,73</t>
+          <t>88,41; 94,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,21; 98,26</t>
+          <t>95,88; 98,4</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95,68</t>
+          <t>95,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90,22</t>
+          <t>90,01</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>92,33</t>
+          <t>92,3</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,76; 99,41</t>
+          <t>95,38; 99,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,72; 97,08</t>
+          <t>89,22; 97,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,74; 99,18</t>
+          <t>94,91; 99,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,0; 97,79</t>
+          <t>92,47; 97,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,15; 97,16</t>
+          <t>91,01; 97,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,97; 92,31</t>
+          <t>82,54; 92,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,11</t>
+          <t>89,35; 96,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,07; 92,36</t>
+          <t>87,16; 92,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>93,85; 97,84</t>
+          <t>93,82; 97,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,4; 93,47</t>
+          <t>87,52; 93,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92,52; 96,99</t>
+          <t>92,71; 96,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,1; 94,07</t>
+          <t>90,02; 93,97</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91,96</t>
+          <t>91,98</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90,09</t>
+          <t>89,88</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,95</t>
+          <t>90,85</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,72; 99,65</t>
+          <t>93,65; 99,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,48; 96,41</t>
+          <t>83,0; 96,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,95; 98,84</t>
+          <t>92,69; 98,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,28; 94,58</t>
+          <t>88,42; 94,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92,6; 97,9</t>
+          <t>92,55; 98,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,72; 93,66</t>
+          <t>81,96; 93,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,23; 98,11</t>
+          <t>86,19; 98,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,68; 92,54</t>
+          <t>86,74; 92,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,58; 98,31</t>
+          <t>94,84; 98,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,06; 93,55</t>
+          <t>85,07; 93,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91,39; 97,95</t>
+          <t>91,15; 97,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88,61; 92,68</t>
+          <t>88,66; 92,67</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98,13</t>
+          <t>98,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,07</t>
+          <t>94,15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,77</t>
+          <t>95,93</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,94; 99,67</t>
+          <t>94,12; 99,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,76; 97,81</t>
+          <t>91,99; 97,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,25; 97,54</t>
+          <t>91,85; 97,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97,04; 98,84</t>
+          <t>97,3; 98,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,31; 97,94</t>
+          <t>93,18; 97,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,01; 96,09</t>
+          <t>91,18; 96,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,35; 97,02</t>
+          <t>93,38; 97,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,97; 95,47</t>
+          <t>92,31; 95,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,61; 98,33</t>
+          <t>95,2; 98,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,69; 96,31</t>
+          <t>92,76; 96,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93,75; 96,94</t>
+          <t>93,79; 96,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,61; 96,71</t>
+          <t>94,68; 96,86</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94,34</t>
+          <t>94,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91,67</t>
+          <t>91,59</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,52; 96,29</t>
+          <t>82,71; 96,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,72; 97,21</t>
+          <t>84,12; 97,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93,06; 99,69</t>
+          <t>92,97; 99,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,92; 96,92</t>
+          <t>90,99; 96,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,81; 96,13</t>
+          <t>80,92; 95,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,75; 94,82</t>
+          <t>86,58; 95,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,16; 95,39</t>
+          <t>87,45; 95,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,59; 93,95</t>
+          <t>87,91; 94,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85,47; 95,18</t>
+          <t>85,28; 95,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,59; 94,97</t>
+          <t>87,44; 95,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91,79; 97,06</t>
+          <t>92,11; 97,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>90,48; 94,57</t>
+          <t>90,15; 94,51</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>87,62</t>
+          <t>87,63</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,35</t>
+          <t>90,31</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95,09; 99,1</t>
+          <t>95,38; 99,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88,26; 97,53</t>
+          <t>88,31; 97,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,2; 94,91</t>
+          <t>85,61; 95,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90,23; 95,29</t>
+          <t>90,39; 95,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,87; 98,03</t>
+          <t>92,18; 98,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84,46; 94,27</t>
+          <t>84,56; 94,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>81,8; 93,13</t>
+          <t>82,27; 93,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,9; 90,83</t>
+          <t>83,63; 90,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94,14; 98,27</t>
+          <t>94,6; 98,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88,35; 95,01</t>
+          <t>88,24; 94,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85,37; 93,18</t>
+          <t>84,55; 92,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>87,89; 92,18</t>
+          <t>87,91; 92,17</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97,22</t>
+          <t>97,25</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>96,92</t>
+          <t>92,21</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>97,0</t>
+          <t>94,63</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,58; 99,47</t>
+          <t>95,28; 99,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88,75; 97,16</t>
+          <t>89,39; 97,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,98; 97,36</t>
+          <t>91,76; 97,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95,8; 98,26</t>
+          <t>95,58; 98,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,98; 98,77</t>
+          <t>93,83; 98,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,9; 95,23</t>
+          <t>89,71; 95,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,03; 94,65</t>
+          <t>89,34; 94,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,42; 99,3</t>
+          <t>89,9; 94,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,73; 98,9</t>
+          <t>95,85; 98,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91,09; 95,47</t>
+          <t>91,03; 95,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,43; 95,24</t>
+          <t>91,35; 95,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,26; 99,03</t>
+          <t>93,23; 95,7</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97,83</t>
+          <t>97,63</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>94,7</t>
+          <t>94,48</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96,08</t>
+          <t>95,85</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>94,07; 97,84</t>
+          <t>93,71; 97,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,66; 98,89</t>
+          <t>94,74; 98,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95,84; 98,68</t>
+          <t>95,68; 98,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96,61; 98,56</t>
+          <t>96,38; 98,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>91,31; 96,29</t>
+          <t>90,9; 96,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,99; 95,48</t>
+          <t>89,82; 95,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,76; 97,57</t>
+          <t>93,44; 97,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>92,71; 95,71</t>
+          <t>92,62; 95,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>93,19; 96,52</t>
+          <t>93,18; 96,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92,6; 96,53</t>
+          <t>92,75; 96,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95,27; 97,68</t>
+          <t>95,24; 97,74</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>95,15; 96,83</t>
+          <t>94,67; 96,8</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96,31</t>
+          <t>96,42</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>93,85</t>
+          <t>92,31</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,8</t>
+          <t>94,13</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>96,43; 98,09</t>
+          <t>96,54; 98,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>93,78; 96,3</t>
+          <t>93,51; 96,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95,22; 97,02</t>
+          <t>95,15; 96,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95,55; 96,93</t>
+          <t>95,72; 96,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>94,39; 96,43</t>
+          <t>94,3; 96,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,75; 92,58</t>
+          <t>89,94; 92,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,21; 94,73</t>
+          <t>92,25; 94,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92,04; 96,69</t>
+          <t>91,45; 93,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>95,54; 96,95</t>
+          <t>95,63; 96,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91,85; 93,82</t>
+          <t>92,0; 93,87</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93,88; 95,48</t>
+          <t>93,97; 95,5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93,89; 96,64</t>
+          <t>93,55; 94,65</t>
         </is>
       </c>
     </row>
